--- a/outputs/183-8.xlsx
+++ b/outputs/183-8.xlsx
@@ -381,284 +381,288 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="71">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="11" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="11" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="12" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="12" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="12" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="12" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="12" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="13" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="12" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="13" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="14" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="14" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="14" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="14" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="15" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="14" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="14" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="15" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="16" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="16" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="16" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="17" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="16" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="16" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="16" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="17" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="17" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="17" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="17" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="17" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="17" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="17" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="5" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="17" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="17" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -914,914 +918,914 @@
   <dimension ref="A1:N1000"/>
   <sheetFormatPr defaultColWidth="14.4296875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="21.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="21.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="8.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="17.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="17.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="15.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="17.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="10.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="14" style="0" width="8.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="21.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="20.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="21.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="8.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="10.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="17.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="17.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="15.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="17.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="10.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="14" style="1" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="H2" s="3" t="s">
+      <c r="A2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="H2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="6" t="n">
+      <c r="C3" s="7" t="n">
         <v>271486433</v>
       </c>
-      <c r="D3" s="7" t="n">
+      <c r="D3" s="8" t="n">
         <v>18.42</v>
       </c>
-      <c r="E3" s="7" t="n">
+      <c r="E3" s="8" t="n">
         <v>96</v>
       </c>
-      <c r="F3" s="7" t="n">
+      <c r="F3" s="8" t="n">
         <v>97.72</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="9" t="n">
+      <c r="I3" s="10" t="n">
         <f aca="false">+SUMIFS($C$1:$C$43,$B$1:$B$43,$H3)</f>
         <v>788949644</v>
       </c>
-      <c r="J3" s="10" t="n">
-        <f aca="false">SUMPRODUCT(($B$1:$B$43=$H3)*N($C$1:$C$43)*N($D$1:$D$43))/SUMPRODUCT(($B$1:$B$43=$H3)*N($C$1:$C$43))</f>
+      <c r="J3" s="11" t="n">
+        <f aca="false">SUMPRODUCT($C$1:$C$43*($B$1:$B$43=$H3),$D$1:$D$43)/SUMIFS($C$1:$C$43,$B$1:$B$43,$H3)</f>
         <v>18.6378159014417</v>
       </c>
-      <c r="K3" s="10" t="n">
-        <f aca="false">SUMPRODUCT(($B$1:$B$43=$H3)*N($C$1:$C$43)*N($E$1:$E$43))/SUMPRODUCT(($B$1:$B$43=$H3)*N($C$1:$C$43))</f>
+      <c r="K3" s="11" t="n">
+        <f aca="false">SUMPRODUCT($C$1:$C$43*($B$1:$B$43=$H3),$E$1:$E$43)/SUMIFS($C$1:$C$43,$B$1:$B$43,$H3)</f>
         <v>95.0531163535451</v>
       </c>
-      <c r="L3" s="10" t="n">
-        <f aca="false">SUMPRODUCT(($B$1:$B$43=$H3)*N($C$1:$C$43)*N($F$1:$F$43))/SUMPRODUCT(($B$1:$B$43=$H3)*N($C$1:$C$43))</f>
+      <c r="L3" s="11" t="n">
+        <f aca="false">SUMPRODUCT($C$1:$C$43*($B$1:$B$43=$H3),$F$1:$F$43)/SUMIFS($C$1:$C$43,$B$1:$B$43,$H3)</f>
         <v>98.7233118299626</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4"/>
-      <c r="B4" s="11" t="s">
+      <c r="A4" s="5"/>
+      <c r="B4" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="12" t="n">
+      <c r="C4" s="13" t="n">
         <v>263336524</v>
       </c>
-      <c r="D4" s="13" t="n">
+      <c r="D4" s="14" t="n">
         <v>17.37</v>
       </c>
-      <c r="E4" s="13" t="n">
+      <c r="E4" s="14" t="n">
         <v>96.98</v>
       </c>
-      <c r="F4" s="13" t="n">
+      <c r="F4" s="14" t="n">
         <v>98.46</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="9" t="n">
+      <c r="I4" s="10" t="n">
         <f aca="false">+SUMIFS($C$1:$C$43,$B$1:$B$43,$H4)</f>
         <v>737002928</v>
       </c>
-      <c r="J4" s="10" t="n">
-        <f aca="false">SUMPRODUCT(($B$1:$B$43=$H4)*N($C$1:$C$43)*N($D$1:$D$43))/SUMPRODUCT(($B$1:$B$43=$H4)*N($C$1:$C$43))</f>
+      <c r="J4" s="11" t="n">
+        <f aca="false">SUMPRODUCT($C$1:$C$43*($B$1:$B$43=$H4),$D$1:$D$43)/SUMIFS($C$1:$C$43,$B$1:$B$43,$H4)</f>
         <v>17.4237656232622</v>
       </c>
-      <c r="K4" s="10" t="n">
-        <f aca="false">SUMPRODUCT(($B$1:$B$43=$H4)*N($C$1:$C$43)*N($E$1:$E$43))/SUMPRODUCT(($B$1:$B$43=$H4)*N($C$1:$C$43))</f>
+      <c r="K4" s="11" t="n">
+        <f aca="false">SUMPRODUCT($C$1:$C$43*($B$1:$B$43=$H4),$E$1:$E$43)/SUMIFS($C$1:$C$43,$B$1:$B$43,$H4)</f>
         <v>94.1759304570768</v>
       </c>
-      <c r="L4" s="10" t="n">
-        <f aca="false">SUMPRODUCT(($B$1:$B$43=$H4)*N($C$1:$C$43)*N($F$1:$F$43))/SUMPRODUCT(($B$1:$B$43=$H4)*N($C$1:$C$43))</f>
+      <c r="L4" s="11" t="n">
+        <f aca="false">SUMPRODUCT($C$1:$C$43*($B$1:$B$43=$H4),$F$1:$F$43)/SUMIFS($C$1:$C$43,$B$1:$B$43,$H4)</f>
         <v>98.858376970885</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4"/>
-      <c r="B5" s="11" t="s">
+      <c r="A5" s="5"/>
+      <c r="B5" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="12" t="n">
+      <c r="C5" s="13" t="n">
         <v>310016060</v>
       </c>
-      <c r="D5" s="13" t="n">
+      <c r="D5" s="14" t="n">
         <v>20.32</v>
       </c>
-      <c r="E5" s="13" t="n">
+      <c r="E5" s="14" t="n">
         <v>97.16</v>
       </c>
-      <c r="F5" s="14" t="n">
+      <c r="F5" s="15" t="n">
         <v>98.56</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="I5" s="9" t="n">
+      <c r="I5" s="10" t="n">
         <f aca="false">+SUMIFS($C$1:$C$43,$B$1:$B$43,$H5)</f>
         <v>897813038</v>
       </c>
-      <c r="J5" s="10" t="n">
-        <f aca="false">SUMPRODUCT(($B$1:$B$43=$H5)*N($C$1:$C$43)*N($D$1:$D$43))/SUMPRODUCT(($B$1:$B$43=$H5)*N($C$1:$C$43))</f>
+      <c r="J5" s="11" t="n">
+        <f aca="false">SUMPRODUCT($C$1:$C$43*($B$1:$B$43=$H5),$D$1:$D$43)/SUMIFS($C$1:$C$43,$B$1:$B$43,$H5)</f>
         <v>23.1486831060171</v>
       </c>
-      <c r="K5" s="10" t="n">
-        <f aca="false">SUMPRODUCT(($B$1:$B$43=$H5)*N($C$1:$C$43)*N($E$1:$E$43))/SUMPRODUCT(($B$1:$B$43=$H5)*N($C$1:$C$43))</f>
+      <c r="K5" s="11" t="n">
+        <f aca="false">SUMPRODUCT($C$1:$C$43*($B$1:$B$43=$H5),$E$1:$E$43)/SUMIFS($C$1:$C$43,$B$1:$B$43,$H5)</f>
         <v>92.4681724660655</v>
       </c>
-      <c r="L5" s="10" t="n">
-        <f aca="false">SUMPRODUCT(($B$1:$B$43=$H5)*N($C$1:$C$43)*N($F$1:$F$43))/SUMPRODUCT(($B$1:$B$43=$H5)*N($C$1:$C$43))</f>
+      <c r="L5" s="11" t="n">
+        <f aca="false">SUMPRODUCT($C$1:$C$43*($B$1:$B$43=$H5),$F$1:$F$43)/SUMIFS($C$1:$C$43,$B$1:$B$43,$H5)</f>
         <v>98.5387964922729</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4"/>
-      <c r="B6" s="15" t="s">
+      <c r="A6" s="5"/>
+      <c r="B6" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>331609915</v>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="18" t="n">
         <v>21.93</v>
       </c>
-      <c r="E6" s="17" t="n">
+      <c r="E6" s="18" t="n">
         <v>98.31</v>
       </c>
-      <c r="F6" s="18" t="n">
+      <c r="F6" s="19" t="n">
         <v>98.61</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="9" t="n">
+      <c r="I6" s="10" t="n">
         <f aca="false">+SUMIFS($C$1:$C$43,$B$1:$B$43,$H6)</f>
         <v>933171553</v>
       </c>
-      <c r="J6" s="10" t="n">
-        <f aca="false">SUMPRODUCT(($B$1:$B$43=$H6)*N($C$1:$C$43)*N($D$1:$D$43))/SUMPRODUCT(($B$1:$B$43=$H6)*N($C$1:$C$43))</f>
+      <c r="J6" s="11" t="n">
+        <f aca="false">SUMPRODUCT($C$1:$C$43*($B$1:$B$43=$H6),$D$1:$D$43)/SUMIFS($C$1:$C$43,$B$1:$B$43,$H6)</f>
         <v>24.8683551691343</v>
       </c>
-      <c r="K6" s="10" t="n">
-        <f aca="false">SUMPRODUCT(($B$1:$B$43=$H6)*N($C$1:$C$43)*N($E$1:$E$43))/SUMPRODUCT(($B$1:$B$43=$H6)*N($C$1:$C$43))</f>
+      <c r="K6" s="11" t="n">
+        <f aca="false">SUMPRODUCT($C$1:$C$43*($B$1:$B$43=$H6),$E$1:$E$43)/SUMIFS($C$1:$C$43,$B$1:$B$43,$H6)</f>
         <v>94.0953099147489</v>
       </c>
-      <c r="L6" s="10" t="n">
-        <f aca="false">SUMPRODUCT(($B$1:$B$43=$H6)*N($C$1:$C$43)*N($F$1:$F$43))/SUMPRODUCT(($B$1:$B$43=$H6)*N($C$1:$C$43))</f>
+      <c r="L6" s="11" t="n">
+        <f aca="false">SUMPRODUCT($C$1:$C$43*($B$1:$B$43=$H6),$F$1:$F$43)/SUMIFS($C$1:$C$43,$B$1:$B$43,$H6)</f>
         <v>98.7126632127675</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="19" t="n">
+      <c r="A7" s="5"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="20" t="n">
         <f aca="false">SUM(C3:C6)</f>
         <v>1176448932</v>
       </c>
-      <c r="D7" s="20" t="n">
+      <c r="D7" s="21" t="n">
         <f aca="false">AVERAGE(D3:D6)</f>
         <v>19.51</v>
       </c>
-      <c r="E7" s="20" t="n">
+      <c r="E7" s="21" t="n">
         <f aca="false">AVERAGE(E3:E6)</f>
         <v>97.1125</v>
       </c>
-      <c r="F7" s="20" t="n">
+      <c r="F7" s="21" t="n">
         <f aca="false">AVERAGE(F3:F6)</f>
         <v>98.3375</v>
       </c>
-      <c r="H7" s="21"/>
-      <c r="I7" s="9" t="n">
+      <c r="H7" s="22"/>
+      <c r="I7" s="10" t="n">
         <f aca="false">SUM(I3:I6)</f>
         <v>3356937163</v>
       </c>
-      <c r="J7" s="10" t="n">
+      <c r="J7" s="11" t="n">
         <f aca="false">AVERAGE(J3:J6)</f>
         <v>21.0196549499639</v>
       </c>
-      <c r="K7" s="10" t="n">
+      <c r="K7" s="11" t="n">
         <f aca="false">AVERAGE(K3:K6)</f>
         <v>93.9481322978591</v>
       </c>
-      <c r="L7" s="10" t="n">
+      <c r="L7" s="11" t="n">
         <f aca="false">AVERAGE(L3:L6)</f>
         <v>98.708287126472</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="22"/>
-      <c r="B8" s="23"/>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="25"/>
+      <c r="A8" s="23"/>
+      <c r="B8" s="24"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="26"/>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="26" t="s">
+      <c r="A9" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="27" t="s">
+      <c r="B9" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="12" t="n">
+      <c r="C9" s="13" t="n">
         <v>3989840</v>
       </c>
-      <c r="D9" s="24" t="n">
+      <c r="D9" s="25" t="n">
         <v>15.18</v>
       </c>
-      <c r="E9" s="13" t="n">
+      <c r="E9" s="14" t="n">
         <v>67.55</v>
       </c>
-      <c r="F9" s="14" t="n">
+      <c r="F9" s="15" t="n">
         <v>92.52</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="26"/>
-      <c r="B10" s="27" t="s">
+      <c r="A10" s="27"/>
+      <c r="B10" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="12" t="n">
+      <c r="C10" s="13" t="n">
         <v>4163703</v>
       </c>
-      <c r="D10" s="24" t="n">
+      <c r="D10" s="25" t="n">
         <v>15.84</v>
       </c>
-      <c r="E10" s="13" t="n">
+      <c r="E10" s="14" t="n">
         <v>86.06</v>
       </c>
-      <c r="F10" s="14" t="n">
+      <c r="F10" s="15" t="n">
         <v>90.85</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="26"/>
-      <c r="B11" s="28" t="s">
+      <c r="A11" s="27"/>
+      <c r="B11" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="12" t="n">
+      <c r="C11" s="13" t="n">
         <v>6184548</v>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="30" t="n">
         <v>23.53</v>
       </c>
-      <c r="E11" s="13" t="n">
+      <c r="E11" s="14" t="n">
         <v>94.57</v>
       </c>
-      <c r="F11" s="14" t="n">
+      <c r="F11" s="15" t="n">
         <v>98.13</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="26"/>
-      <c r="B12" s="30" t="s">
+      <c r="A12" s="27"/>
+      <c r="B12" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="12" t="n">
+      <c r="C12" s="13" t="n">
         <v>6066779</v>
       </c>
-      <c r="D12" s="29" t="n">
+      <c r="D12" s="30" t="n">
         <v>23.33</v>
       </c>
-      <c r="E12" s="13" t="n">
+      <c r="E12" s="14" t="n">
         <v>87.39</v>
       </c>
-      <c r="F12" s="14" t="n">
+      <c r="F12" s="15" t="n">
         <v>94.65</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="26"/>
-      <c r="B13" s="30"/>
-      <c r="C13" s="31" t="n">
+      <c r="A13" s="27"/>
+      <c r="B13" s="31"/>
+      <c r="C13" s="32" t="n">
         <f aca="false">SUM(C9:C12)</f>
         <v>20404870</v>
       </c>
-      <c r="D13" s="32" t="n">
+      <c r="D13" s="33" t="n">
         <f aca="false">AVERAGE(D9:D12)</f>
         <v>19.47</v>
       </c>
-      <c r="E13" s="32" t="n">
+      <c r="E13" s="33" t="n">
         <f aca="false">AVERAGE(E9:E12)</f>
         <v>83.8925</v>
       </c>
-      <c r="F13" s="32" t="n">
+      <c r="F13" s="33" t="n">
         <f aca="false">AVERAGE(F9:F12)</f>
         <v>94.0375</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="22"/>
-      <c r="B14" s="23"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="25"/>
+      <c r="A14" s="23"/>
+      <c r="B14" s="24"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="26"/>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="33" t="s">
+      <c r="A15" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="27" t="s">
+      <c r="B15" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="12" t="n">
+      <c r="C15" s="13" t="n">
         <v>20750626</v>
       </c>
-      <c r="D15" s="34" t="n">
+      <c r="D15" s="35" t="n">
         <v>15.98</v>
       </c>
-      <c r="E15" s="35" t="n">
+      <c r="E15" s="36" t="n">
         <v>98.22</v>
       </c>
-      <c r="F15" s="36" t="n">
+      <c r="F15" s="37" t="n">
         <v>99.31</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="33"/>
-      <c r="B16" s="27" t="s">
+      <c r="A16" s="34"/>
+      <c r="B16" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="12" t="n">
+      <c r="C16" s="13" t="n">
         <v>17783965</v>
       </c>
-      <c r="D16" s="34" t="n">
+      <c r="D16" s="35" t="n">
         <v>13.69</v>
       </c>
-      <c r="E16" s="35" t="n">
+      <c r="E16" s="36" t="n">
         <v>96.91</v>
       </c>
-      <c r="F16" s="36" t="n">
+      <c r="F16" s="37" t="n">
         <v>98.46</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="33"/>
-      <c r="B17" s="37" t="s">
+      <c r="A17" s="34"/>
+      <c r="B17" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="12" t="n">
+      <c r="C17" s="13" t="n">
         <v>23874411</v>
       </c>
-      <c r="D17" s="35" t="n">
+      <c r="D17" s="36" t="n">
         <v>18.535</v>
       </c>
-      <c r="E17" s="35" t="n">
+      <c r="E17" s="36" t="n">
         <v>97.09</v>
       </c>
-      <c r="F17" s="36" t="n">
+      <c r="F17" s="37" t="n">
         <v>98.015</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="33"/>
-      <c r="B18" s="38" t="s">
+      <c r="A18" s="34"/>
+      <c r="B18" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="12" t="n">
+      <c r="C18" s="13" t="n">
         <v>24681196</v>
       </c>
-      <c r="D18" s="35" t="n">
+      <c r="D18" s="36" t="n">
         <v>19.295</v>
       </c>
-      <c r="E18" s="35" t="n">
+      <c r="E18" s="36" t="n">
         <v>97.615</v>
       </c>
-      <c r="F18" s="36" t="n">
+      <c r="F18" s="37" t="n">
         <v>97.91</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="33"/>
-      <c r="B19" s="38"/>
-      <c r="C19" s="31" t="n">
+      <c r="A19" s="34"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="32" t="n">
         <f aca="false">SUM(C15:C18)</f>
         <v>87090198</v>
       </c>
-      <c r="D19" s="39" t="n">
+      <c r="D19" s="40" t="n">
         <f aca="false">AVERAGE(D15:D18)</f>
         <v>16.875</v>
       </c>
-      <c r="E19" s="39" t="n">
+      <c r="E19" s="40" t="n">
         <f aca="false">AVERAGE(E15:E18)</f>
         <v>97.45875</v>
       </c>
-      <c r="F19" s="39" t="n">
+      <c r="F19" s="40" t="n">
         <f aca="false">AVERAGE(F15:F18)</f>
         <v>98.42375</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="22"/>
-      <c r="B20" s="23"/>
-      <c r="C20" s="24"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="25"/>
+      <c r="A20" s="23"/>
+      <c r="B20" s="24"/>
+      <c r="C20" s="25"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="26"/>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="40" t="s">
+      <c r="A21" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="B21" s="41" t="s">
+      <c r="B21" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="12" t="n">
+      <c r="C21" s="13" t="n">
         <v>5556478</v>
       </c>
-      <c r="D21" s="42" t="n">
+      <c r="D21" s="43" t="n">
         <v>14.92</v>
       </c>
-      <c r="E21" s="13" t="n">
+      <c r="E21" s="14" t="n">
         <v>98.66</v>
       </c>
-      <c r="F21" s="14" t="n">
+      <c r="F21" s="15" t="n">
         <v>99.61</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="40"/>
-      <c r="B22" s="41" t="s">
+      <c r="A22" s="41"/>
+      <c r="B22" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="12" t="n">
+      <c r="C22" s="13" t="n">
         <v>5374893</v>
       </c>
-      <c r="D22" s="42" t="n">
+      <c r="D22" s="43" t="n">
         <v>14.44</v>
       </c>
-      <c r="E22" s="13" t="n">
+      <c r="E22" s="14" t="n">
         <v>99.49</v>
       </c>
-      <c r="F22" s="14" t="n">
+      <c r="F22" s="15" t="n">
         <v>99.3</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="40"/>
-      <c r="B23" s="43" t="s">
+      <c r="A23" s="41"/>
+      <c r="B23" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="12" t="n">
+      <c r="C23" s="13" t="n">
         <v>7204872</v>
       </c>
-      <c r="D23" s="13" t="n">
+      <c r="D23" s="14" t="n">
         <v>19.29</v>
       </c>
-      <c r="E23" s="13" t="n">
+      <c r="E23" s="14" t="n">
         <v>98.1</v>
       </c>
-      <c r="F23" s="44" t="n">
+      <c r="F23" s="45" t="n">
         <v>99.91</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="40"/>
-      <c r="B24" s="45" t="s">
+      <c r="A24" s="41"/>
+      <c r="B24" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="12" t="n">
+      <c r="C24" s="13" t="n">
         <v>6944925</v>
       </c>
-      <c r="D24" s="13" t="n">
+      <c r="D24" s="14" t="n">
         <v>18.65</v>
       </c>
-      <c r="E24" s="13" t="n">
+      <c r="E24" s="14" t="n">
         <v>97.25</v>
       </c>
-      <c r="F24" s="44" t="n">
+      <c r="F24" s="45" t="n">
         <v>99.53</v>
       </c>
-      <c r="J24" s="46"/>
-      <c r="K24" s="46"/>
-      <c r="M24" s="47"/>
-      <c r="N24" s="47"/>
+      <c r="J24" s="47"/>
+      <c r="K24" s="47"/>
+      <c r="M24" s="48"/>
+      <c r="N24" s="48"/>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="40"/>
-      <c r="B25" s="45"/>
-      <c r="C25" s="31" t="n">
+      <c r="A25" s="41"/>
+      <c r="B25" s="46"/>
+      <c r="C25" s="32" t="n">
         <f aca="false">SUM(C21:C24)</f>
         <v>25081168</v>
       </c>
-      <c r="D25" s="32" t="n">
+      <c r="D25" s="33" t="n">
         <f aca="false">AVERAGE(D21:D24)</f>
         <v>16.825</v>
       </c>
-      <c r="E25" s="32" t="n">
+      <c r="E25" s="33" t="n">
         <f aca="false">AVERAGE(E21:E24)</f>
         <v>98.375</v>
       </c>
-      <c r="F25" s="32" t="n">
+      <c r="F25" s="33" t="n">
         <f aca="false">AVERAGE(F21:F24)</f>
         <v>99.5875</v>
       </c>
-      <c r="J25" s="46"/>
-      <c r="K25" s="46"/>
-      <c r="M25" s="47"/>
-      <c r="N25" s="47"/>
+      <c r="J25" s="47"/>
+      <c r="K25" s="47"/>
+      <c r="M25" s="48"/>
+      <c r="N25" s="48"/>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="22"/>
-      <c r="B26" s="23"/>
-      <c r="C26" s="24"/>
-      <c r="D26" s="24"/>
-      <c r="E26" s="24"/>
-      <c r="F26" s="25"/>
-      <c r="J26" s="46"/>
-      <c r="K26" s="46"/>
-      <c r="L26" s="46"/>
-      <c r="M26" s="47"/>
-      <c r="N26" s="47"/>
+      <c r="A26" s="23"/>
+      <c r="B26" s="24"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="26"/>
+      <c r="J26" s="47"/>
+      <c r="K26" s="47"/>
+      <c r="L26" s="47"/>
+      <c r="M26" s="48"/>
+      <c r="N26" s="48"/>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="48" t="s">
+      <c r="A27" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="B27" s="49" t="s">
+      <c r="B27" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="C27" s="12" t="n">
+      <c r="C27" s="13" t="n">
         <v>73498259</v>
       </c>
-      <c r="D27" s="29" t="n">
+      <c r="D27" s="30" t="n">
         <v>15.31</v>
       </c>
-      <c r="E27" s="29" t="n">
+      <c r="E27" s="30" t="n">
         <v>95.55</v>
       </c>
-      <c r="F27" s="50" t="n">
+      <c r="F27" s="51" t="n">
         <v>99.12</v>
       </c>
-      <c r="J27" s="46"/>
-      <c r="K27" s="46"/>
-      <c r="L27" s="46"/>
-      <c r="M27" s="47"/>
-      <c r="N27" s="47"/>
+      <c r="J27" s="47"/>
+      <c r="K27" s="47"/>
+      <c r="L27" s="47"/>
+      <c r="M27" s="48"/>
+      <c r="N27" s="48"/>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="48"/>
-      <c r="B28" s="49" t="s">
+      <c r="A28" s="49"/>
+      <c r="B28" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="C28" s="12" t="n">
+      <c r="C28" s="13" t="n">
         <v>53345907</v>
       </c>
-      <c r="D28" s="29" t="n">
+      <c r="D28" s="30" t="n">
         <v>11.33</v>
       </c>
-      <c r="E28" s="29" t="n">
+      <c r="E28" s="30" t="n">
         <v>79.93</v>
       </c>
-      <c r="F28" s="50" t="n">
+      <c r="F28" s="51" t="n">
         <v>98.71</v>
       </c>
-      <c r="J28" s="46"/>
-      <c r="K28" s="46"/>
-      <c r="L28" s="46"/>
-      <c r="M28" s="47"/>
-      <c r="N28" s="47"/>
+      <c r="J28" s="47"/>
+      <c r="K28" s="47"/>
+      <c r="L28" s="47"/>
+      <c r="M28" s="48"/>
+      <c r="N28" s="48"/>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="48"/>
-      <c r="B29" s="51" t="s">
+      <c r="A29" s="49"/>
+      <c r="B29" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="C29" s="12" t="n">
+      <c r="C29" s="13" t="n">
         <v>78709006</v>
       </c>
-      <c r="D29" s="13" t="n">
+      <c r="D29" s="14" t="n">
         <v>16.1725</v>
       </c>
-      <c r="E29" s="13" t="n">
+      <c r="E29" s="14" t="n">
         <v>84.615</v>
       </c>
-      <c r="F29" s="14" t="n">
+      <c r="F29" s="15" t="n">
         <v>97.7</v>
       </c>
-      <c r="J29" s="46"/>
-      <c r="K29" s="46"/>
-      <c r="L29" s="46"/>
-      <c r="M29" s="47"/>
-      <c r="N29" s="47"/>
+      <c r="J29" s="47"/>
+      <c r="K29" s="47"/>
+      <c r="L29" s="47"/>
+      <c r="M29" s="48"/>
+      <c r="N29" s="48"/>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="48"/>
-      <c r="B30" s="52" t="s">
+      <c r="A30" s="49"/>
+      <c r="B30" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="C30" s="12" t="n">
+      <c r="C30" s="13" t="n">
         <v>87916088</v>
       </c>
-      <c r="D30" s="29" t="n">
+      <c r="D30" s="30" t="n">
         <v>21.61</v>
       </c>
-      <c r="E30" s="29" t="n">
+      <c r="E30" s="30" t="n">
         <v>97.15</v>
       </c>
-      <c r="F30" s="50" t="n">
+      <c r="F30" s="51" t="n">
         <v>99.07</v>
       </c>
-      <c r="J30" s="46"/>
-      <c r="K30" s="46"/>
-      <c r="L30" s="46"/>
-      <c r="M30" s="47"/>
-      <c r="N30" s="47"/>
+      <c r="J30" s="47"/>
+      <c r="K30" s="47"/>
+      <c r="L30" s="47"/>
+      <c r="M30" s="48"/>
+      <c r="N30" s="48"/>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="48"/>
-      <c r="B31" s="52"/>
-      <c r="C31" s="31" t="n">
+      <c r="A31" s="49"/>
+      <c r="B31" s="53"/>
+      <c r="C31" s="32" t="n">
         <f aca="false">SUM(C27:C30)</f>
         <v>293469260</v>
       </c>
-      <c r="D31" s="32" t="n">
+      <c r="D31" s="33" t="n">
         <f aca="false">AVERAGE(D27:D30)</f>
         <v>16.105625</v>
       </c>
-      <c r="E31" s="32" t="n">
+      <c r="E31" s="33" t="n">
         <f aca="false">AVERAGE(E27:E30)</f>
         <v>89.31125</v>
       </c>
-      <c r="F31" s="32" t="n">
+      <c r="F31" s="33" t="n">
         <f aca="false">AVERAGE(F27:F30)</f>
         <v>98.65</v>
       </c>
-      <c r="J31" s="46"/>
-      <c r="K31" s="46"/>
-      <c r="L31" s="53"/>
-      <c r="M31" s="47"/>
-      <c r="N31" s="47"/>
+      <c r="J31" s="47"/>
+      <c r="K31" s="47"/>
+      <c r="L31" s="54"/>
+      <c r="M31" s="48"/>
+      <c r="N31" s="48"/>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="54"/>
-      <c r="B32" s="55"/>
-      <c r="C32" s="24"/>
-      <c r="D32" s="24"/>
-      <c r="E32" s="24"/>
-      <c r="F32" s="25"/>
-      <c r="J32" s="46"/>
-      <c r="K32" s="46"/>
-      <c r="L32" s="47"/>
-      <c r="M32" s="47"/>
-      <c r="N32" s="47"/>
+      <c r="A32" s="55"/>
+      <c r="B32" s="56"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="26"/>
+      <c r="J32" s="47"/>
+      <c r="K32" s="47"/>
+      <c r="L32" s="48"/>
+      <c r="M32" s="48"/>
+      <c r="N32" s="48"/>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="56" t="s">
+      <c r="A33" s="57" t="s">
         <v>16</v>
       </c>
-      <c r="B33" s="57" t="s">
+      <c r="B33" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="C33" s="12" t="n">
+      <c r="C33" s="13" t="n">
         <v>182867835</v>
       </c>
-      <c r="D33" s="13" t="n">
+      <c r="D33" s="14" t="n">
         <v>22.25</v>
       </c>
-      <c r="E33" s="13" t="n">
+      <c r="E33" s="14" t="n">
         <v>98.77</v>
       </c>
-      <c r="F33" s="14" t="n">
+      <c r="F33" s="15" t="n">
         <v>99.38</v>
       </c>
-      <c r="L33" s="47"/>
-      <c r="M33" s="47"/>
+      <c r="L33" s="48"/>
+      <c r="M33" s="48"/>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="56"/>
-      <c r="B34" s="57" t="s">
+      <c r="A34" s="57"/>
+      <c r="B34" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="C34" s="12" t="n">
+      <c r="C34" s="13" t="n">
         <v>164654673</v>
       </c>
-      <c r="D34" s="13" t="n">
+      <c r="D34" s="14" t="n">
         <v>20.03</v>
       </c>
-      <c r="E34" s="13" t="n">
+      <c r="E34" s="14" t="n">
         <v>97.99</v>
       </c>
-      <c r="F34" s="14" t="n">
+      <c r="F34" s="15" t="n">
         <v>99.19</v>
       </c>
-      <c r="L34" s="47"/>
-      <c r="M34" s="47"/>
+      <c r="L34" s="48"/>
+      <c r="M34" s="48"/>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="56"/>
-      <c r="B35" s="58" t="s">
+      <c r="A35" s="57"/>
+      <c r="B35" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="C35" s="12" t="n">
+      <c r="C35" s="13" t="n">
         <v>169183110</v>
       </c>
-      <c r="D35" s="13" t="n">
+      <c r="D35" s="14" t="n">
         <v>33.365</v>
       </c>
-      <c r="E35" s="13" t="n">
+      <c r="E35" s="14" t="n">
         <v>84.9533333333333</v>
       </c>
-      <c r="F35" s="14" t="n">
+      <c r="F35" s="15" t="n">
         <v>98.9833333333333</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="56"/>
-      <c r="B36" s="59" t="s">
+      <c r="A36" s="57"/>
+      <c r="B36" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="C36" s="12" t="n">
+      <c r="C36" s="13" t="n">
         <v>179219495</v>
       </c>
-      <c r="D36" s="13" t="n">
+      <c r="D36" s="14" t="n">
         <v>35.6933333333333</v>
       </c>
-      <c r="E36" s="13" t="n">
+      <c r="E36" s="14" t="n">
         <v>85.64</v>
       </c>
-      <c r="F36" s="14" t="n">
+      <c r="F36" s="15" t="n">
         <v>99.0433333333333</v>
       </c>
-      <c r="L36" s="47"/>
+      <c r="L36" s="48"/>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="56"/>
-      <c r="B37" s="59"/>
-      <c r="C37" s="31" t="n">
+      <c r="A37" s="57"/>
+      <c r="B37" s="60"/>
+      <c r="C37" s="32" t="n">
         <f aca="false">SUM(C33:C36)</f>
         <v>695925113</v>
       </c>
-      <c r="D37" s="32" t="n">
+      <c r="D37" s="33" t="n">
         <f aca="false">AVERAGE(D33:D36)</f>
         <v>27.8345833333333</v>
       </c>
-      <c r="E37" s="32" t="n">
+      <c r="E37" s="33" t="n">
         <f aca="false">AVERAGE(E33:E36)</f>
         <v>91.8383333333333</v>
       </c>
-      <c r="F37" s="32" t="n">
+      <c r="F37" s="33" t="n">
         <f aca="false">AVERAGE(F33:F36)</f>
         <v>99.1491666666667</v>
       </c>
-      <c r="L37" s="47"/>
+      <c r="L37" s="48"/>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="22"/>
-      <c r="B38" s="23"/>
-      <c r="C38" s="24"/>
-      <c r="D38" s="24"/>
-      <c r="E38" s="24"/>
-      <c r="F38" s="25"/>
-      <c r="L38" s="47"/>
+      <c r="A38" s="23"/>
+      <c r="B38" s="24"/>
+      <c r="C38" s="25"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="25"/>
+      <c r="F38" s="26"/>
+      <c r="L38" s="48"/>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="60" t="s">
+      <c r="A39" s="61" t="s">
         <v>17</v>
       </c>
-      <c r="B39" s="61" t="s">
+      <c r="B39" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="C39" s="12" t="n">
+      <c r="C39" s="13" t="n">
         <v>230800173</v>
       </c>
-      <c r="D39" s="13" t="n">
+      <c r="D39" s="14" t="n">
         <v>17.48</v>
       </c>
-      <c r="E39" s="13" t="n">
+      <c r="E39" s="14" t="n">
         <v>90.94</v>
       </c>
-      <c r="F39" s="14" t="n">
+      <c r="F39" s="15" t="n">
         <v>99.29</v>
       </c>
-      <c r="K39" s="47"/>
-      <c r="L39" s="47"/>
+      <c r="K39" s="48"/>
+      <c r="L39" s="48"/>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="60"/>
-      <c r="B40" s="61" t="s">
+      <c r="A40" s="61"/>
+      <c r="B40" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="C40" s="12" t="n">
+      <c r="C40" s="13" t="n">
         <v>228343263</v>
       </c>
-      <c r="D40" s="13" t="n">
+      <c r="D40" s="14" t="n">
         <v>17.42</v>
       </c>
-      <c r="E40" s="13" t="n">
+      <c r="E40" s="14" t="n">
         <v>91.33</v>
       </c>
-      <c r="F40" s="14" t="n">
+      <c r="F40" s="15" t="n">
         <v>99.28</v>
       </c>
-      <c r="K40" s="47"/>
-      <c r="L40" s="47"/>
+      <c r="K40" s="48"/>
+      <c r="L40" s="48"/>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="60"/>
-      <c r="B41" s="62" t="s">
+      <c r="A41" s="61"/>
+      <c r="B41" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="C41" s="12" t="n">
+      <c r="C41" s="13" t="n">
         <v>302641031</v>
       </c>
-      <c r="D41" s="13" t="n">
+      <c r="D41" s="14" t="n">
         <v>22.5975</v>
       </c>
-      <c r="E41" s="13" t="n">
+      <c r="E41" s="14" t="n">
         <v>93.36375</v>
       </c>
-      <c r="F41" s="14" t="n">
+      <c r="F41" s="15" t="n">
         <v>98.50375</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="60"/>
-      <c r="B42" s="63" t="s">
+      <c r="A42" s="61"/>
+      <c r="B42" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="C42" s="64" t="n">
+      <c r="C42" s="65" t="n">
         <v>296733155</v>
       </c>
-      <c r="D42" s="65" t="n">
+      <c r="D42" s="66" t="n">
         <v>23.22</v>
       </c>
-      <c r="E42" s="65" t="n">
+      <c r="E42" s="66" t="n">
         <v>93.3575</v>
       </c>
-      <c r="F42" s="66" t="n">
+      <c r="F42" s="67" t="n">
         <v>98.6525</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="60"/>
-      <c r="B43" s="67"/>
-      <c r="C43" s="68" t="n">
+      <c r="A43" s="61"/>
+      <c r="B43" s="68"/>
+      <c r="C43" s="69" t="n">
         <f aca="false">SUM(C39:C42)</f>
         <v>1058517622</v>
       </c>
-      <c r="D43" s="69" t="n">
+      <c r="D43" s="70" t="n">
         <f aca="false">AVERAGE(D39:D42)</f>
         <v>20.179375</v>
       </c>
-      <c r="E43" s="69" t="n">
+      <c r="E43" s="70" t="n">
         <f aca="false">AVERAGE(E39:E42)</f>
         <v>92.2478125</v>
       </c>
-      <c r="F43" s="69" t="n">
+      <c r="F43" s="70" t="n">
         <f aca="false">AVERAGE(F39:F42)</f>
         <v>98.9315625</v>
       </c>
